--- a/mari_poc/results/experiment_log.xlsx
+++ b/mari_poc/results/experiment_log.xlsx
@@ -428,13 +428,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S57"/>
+  <dimension ref="A1:S71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="31" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
@@ -449,7 +449,7 @@
     <col width="15" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
     <col width="22" customWidth="1" min="18" max="18"/>
-    <col width="36" customWidth="1" min="19" max="19"/>
+    <col width="40" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -555,7 +555,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-04-24T17:27:39.244662</t>
+          <t>2026-04-26T00:22:12.596470</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-04-24T17:27:39.453799</t>
+          <t>2026-04-26T00:22:12.803623</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-04-24T17:27:39.653724</t>
+          <t>2026-04-26T00:22:13.006961</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-04-24T17:27:39.865498</t>
+          <t>2026-04-26T00:22:13.216868</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-04-24T17:27:40.073407</t>
+          <t>2026-04-26T00:22:13.427121</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-04-24T17:27:40.275822</t>
+          <t>2026-04-26T00:22:13.637119</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-04-24T17:27:40.486389</t>
+          <t>2026-04-26T00:22:13.841005</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-04-24T17:27:40.687797</t>
+          <t>2026-04-26T00:22:14.045475</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-04-24T17:27:40.901205</t>
+          <t>2026-04-26T00:22:14.255495</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-04-24T17:27:41.111696</t>
+          <t>2026-04-26T00:22:14.459875</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-04-24T17:27:41.321583</t>
+          <t>2026-04-26T00:22:14.665147</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-04-24T17:27:41.527161</t>
+          <t>2026-04-26T00:22:14.869949</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-04-24T17:27:41.768716</t>
+          <t>2026-04-26T00:22:15.108943</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-04-24T17:27:41.974507</t>
+          <t>2026-04-26T00:22:15.316932</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-04-24T17:27:42.184653</t>
+          <t>2026-04-26T00:22:15.530465</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-04-24T17:27:42.385846</t>
+          <t>2026-04-26T00:22:15.734836</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-04-24T17:27:42.585209</t>
+          <t>2026-04-26T00:22:15.935558</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-04-24T17:27:42.729401</t>
+          <t>2026-04-26T00:22:16.087252</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-04-24T17:27:42.952531</t>
+          <t>2026-04-26T00:22:16.314321</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-04-24T17:27:43.161833</t>
+          <t>2026-04-26T00:22:16.521859</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1971,7 +1971,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-04-24T17:27:43.369661</t>
+          <t>2026-04-26T00:22:16.732367</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-04-24T17:27:43.565408</t>
+          <t>2026-04-26T00:22:16.927812</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-04-24T17:27:43.634085</t>
+          <t>2026-04-26T00:22:16.999517</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-04-24T17:27:43.639559</t>
+          <t>2026-04-26T00:22:17.005019</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-04-24T17:27:43.706888</t>
+          <t>2026-04-26T00:22:17.073495</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-04-24T17:27:44.017592</t>
+          <t>2026-04-26T00:22:17.383245</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-04-24T17:27:45.426854</t>
+          <t>2026-04-26T00:22:18.764074</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-04-24T17:27:47.362005</t>
+          <t>2026-04-26T00:22:20.675073</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2507,7 +2507,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-04-24T17:27:47.870413</t>
+          <t>2026-04-26T00:22:21.209220</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-04-24T17:27:48.087114</t>
+          <t>2026-04-26T00:22:21.423080</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-04-24T17:27:48.308376</t>
+          <t>2026-04-26T00:22:21.650017</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-04-24T17:27:48.551026</t>
+          <t>2026-04-26T00:22:21.890864</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-04-24T17:27:48.803165</t>
+          <t>2026-04-26T00:22:22.141932</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-04-24T17:27:49.063664</t>
+          <t>2026-04-26T00:22:22.403478</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2933,7 +2933,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-04-24T17:27:49.334997</t>
+          <t>2026-04-26T00:22:22.671526</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3004,7 +3004,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-04-24T17:27:49.617223</t>
+          <t>2026-04-26T00:22:22.945806</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-04-24T17:27:49.831716</t>
+          <t>2026-04-26T00:22:23.159862</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-04-24T17:27:50.045891</t>
+          <t>2026-04-26T00:22:23.372639</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-04-24T17:27:50.266020</t>
+          <t>2026-04-26T00:22:23.594333</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-04-24T17:27:50.497799</t>
+          <t>2026-04-26T00:22:23.820163</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-04-24T17:27:50.774328</t>
+          <t>2026-04-26T00:22:24.098673</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-04-24T17:27:51.027781</t>
+          <t>2026-04-26T00:22:24.351335</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-04-24T17:27:51.291316</t>
+          <t>2026-04-26T00:22:24.613784</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3572,7 +3572,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-04-24T17:27:51.562662</t>
+          <t>2026-04-26T00:22:24.881256</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3643,7 +3643,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-04-24T17:27:51.776233</t>
+          <t>2026-04-26T00:22:25.099956</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-04-24T17:27:51.997475</t>
+          <t>2026-04-26T00:22:25.312572</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-04-24T17:27:52.221556</t>
+          <t>2026-04-26T00:22:25.540704</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-04-24T17:27:52.469500</t>
+          <t>2026-04-26T00:22:25.780114</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3927,7 +3927,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-04-24T17:27:52.719755</t>
+          <t>2026-04-26T00:22:26.023100</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3998,7 +3998,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-04-24T17:27:52.972577</t>
+          <t>2026-04-26T00:22:26.280344</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-04-24T17:27:53.238532</t>
+          <t>2026-04-26T00:22:26.540183</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4140,7 +4140,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-04-24T17:28:40.974415</t>
+          <t>2026-04-26T00:23:14.095748</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-04-24T17:28:41.427695</t>
+          <t>2026-04-26T00:23:14.528932</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-04-24T17:28:41.759880</t>
+          <t>2026-04-26T00:23:14.846687</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4349,7 +4349,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-04-24T17:28:42.080188</t>
+          <t>2026-04-26T00:23:15.166701</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-04-24T17:28:42.400293</t>
+          <t>2026-04-26T00:23:15.488613</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4478,6 +4478,948 @@
       <c r="S57" t="inlineStr">
         <is>
           <t>thr=10,11 events</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-04-26T00:23:16.071641</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>holdout_vintage_transfer</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Cox</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>n_wells_producing_at_spud, spud_year, field_cum_gas_at_spud, gas_rate_cv_yr12, peak_gas_rate</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>5</v>
+      </c>
+      <c r="H58" t="n">
+        <v>16</v>
+      </c>
+      <c r="I58" t="n">
+        <v>12</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="n">
+        <v>379</v>
+      </c>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>M-E-2-HRL</t>
+        </is>
+      </c>
+      <c r="R58" t="n">
+        <v>102</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>Train pre-2000, test post-2000. MAE(events)=32</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-04-26T00:23:16.076221</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>holdout_decade_1978-1989</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Cox</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>n_wells_producing_at_spud, spud_year, field_cum_gas_at_spud, gas_rate_cv_yr12, peak_gas_rate</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>5</v>
+      </c>
+      <c r="H59" t="n">
+        <v>16</v>
+      </c>
+      <c r="I59" t="n">
+        <v>12</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="n">
+        <v>0.611</v>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="n">
+        <v>299</v>
+      </c>
+      <c r="O59" t="n">
+        <v>379</v>
+      </c>
+      <c r="P59" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>M-11-HRL</t>
+        </is>
+      </c>
+      <c r="R59" t="n">
+        <v>791</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>Stratified LOO, 1978-1989 cohort only</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-04-26T00:23:16.079172</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>holdout_decade_1990-1999</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Cox</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>n_wells_producing_at_spud, spud_year, field_cum_gas_at_spud, gas_rate_cv_yr12, peak_gas_rate</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>5</v>
+      </c>
+      <c r="H60" t="n">
+        <v>16</v>
+      </c>
+      <c r="I60" t="n">
+        <v>12</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="n">
+        <v>0.738</v>
+      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="n">
+        <v>379</v>
+      </c>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>M-67-HRL</t>
+        </is>
+      </c>
+      <c r="R60" t="n">
+        <v>214</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>Stratified LOO, 1990-1999 cohort only</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-04-26T00:23:16.080908</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>holdout_decade_2000+</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Cox</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>n_wells_producing_at_spud, spud_year, field_cum_gas_at_spud, gas_rate_cv_yr12, peak_gas_rate</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>5</v>
+      </c>
+      <c r="H61" t="n">
+        <v>16</v>
+      </c>
+      <c r="I61" t="n">
+        <v>12</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="n">
+        <v>379</v>
+      </c>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>M-E-2-HRL</t>
+        </is>
+      </c>
+      <c r="R61" t="n">
+        <v>90</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>Stratified LOO, 2000+ cohort only</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-04-26T00:23:16.272799</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>holdout_no_surprises_loocv</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Cox</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>n_wells_producing_at_spud, spud_year, field_cum_gas_at_spud, gas_rate_cv_yr12, peak_gas_rate</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>5</v>
+      </c>
+      <c r="H62" t="n">
+        <v>12</v>
+      </c>
+      <c r="I62" t="n">
+        <v>8</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="n">
+        <v>0.769</v>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="n">
+        <v>329</v>
+      </c>
+      <c r="O62" t="n">
+        <v>379</v>
+      </c>
+      <c r="P62" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>M-11-HRL</t>
+        </is>
+      </c>
+      <c r="R62" t="n">
+        <v>791</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>12-well LOOCV without surprises</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-04-26T00:23:16.273602</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>holdout_surprise_test</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Cox</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>n_wells_producing_at_spud, spud_year, field_cum_gas_at_spud, gas_rate_cv_yr12, peak_gas_rate</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>5</v>
+      </c>
+      <c r="H63" t="n">
+        <v>16</v>
+      </c>
+      <c r="I63" t="n">
+        <v>12</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="n">
+        <v>379</v>
+      </c>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>M-67-HRL</t>
+        </is>
+      </c>
+      <c r="R63" t="n">
+        <v>230</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>4 surprise wells predicted from clean12. MAE=210</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-04-26T00:23:16.293075</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>holdout_extreme_feature</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Cox</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>n_wells_producing_at_spud, spud_year, field_cum_gas_at_spud, gas_rate_cv_yr12, peak_gas_rate</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>5</v>
+      </c>
+      <c r="H64" t="n">
+        <v>16</v>
+      </c>
+      <c r="I64" t="n">
+        <v>12</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="n">
+        <v>379</v>
+      </c>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>M-11-HRL</t>
+        </is>
+      </c>
+      <c r="R64" t="n">
+        <v>791</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>Extreme n_wells_producing_at_spud holdout (4 wells). MAE=400</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-04-26T00:23:17.139819</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>8.6</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>calibration_ibs</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Cox</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>n_wells_producing_at_spud, spud_year, field_cum_gas_at_spud, gas_rate_cv_yr12, peak_gas_rate</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>5</v>
+      </c>
+      <c r="H65" t="n">
+        <v>16</v>
+      </c>
+      <c r="I65" t="n">
+        <v>12</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="n">
+        <v>0.788</v>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="n">
+        <v>299</v>
+      </c>
+      <c r="O65" t="n">
+        <v>379</v>
+      </c>
+      <c r="P65" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>M-11-HRL</t>
+        </is>
+      </c>
+      <c r="R65" t="n">
+        <v>791</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>IBS=0.0808, ratio=0.421</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-04-26T00:23:17.142907</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>8.6</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>calibration_td_auc</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Cox</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>n_wells_producing_at_spud, spud_year, field_cum_gas_at_spud, gas_rate_cv_yr12, peak_gas_rate</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>5</v>
+      </c>
+      <c r="H66" t="n">
+        <v>16</v>
+      </c>
+      <c r="I66" t="n">
+        <v>12</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="n">
+        <v>0.788</v>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="n">
+        <v>299</v>
+      </c>
+      <c r="O66" t="n">
+        <v>379</v>
+      </c>
+      <c r="P66" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>M-11-HRL</t>
+        </is>
+      </c>
+      <c r="R66" t="n">
+        <v>791</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>AUC@60=0.949,@120=0.896,@240=0.980</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-04-26T00:23:17.143728</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>8.6</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>calibration_post2000</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Cox</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>n_wells_producing_at_spud, spud_year, field_cum_gas_at_spud, gas_rate_cv_yr12, peak_gas_rate</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>5</v>
+      </c>
+      <c r="H67" t="n">
+        <v>16</v>
+      </c>
+      <c r="I67" t="n">
+        <v>12</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="n">
+        <v>379</v>
+      </c>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>M-E-2-HRL</t>
+        </is>
+      </c>
+      <c r="R67" t="n">
+        <v>102</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>Post-2000 C=0.500, bias=-32mo</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-04-26T00:23:17.605565</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>8.7</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>flag_flag_pre_1993_replace_n_wells_producing_at_spud</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Cox</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>flag_pre_1993, spud_year, field_cum_gas_at_spud, gas_rate_cv_yr12, peak_gas_rate</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>5</v>
+      </c>
+      <c r="H68" t="n">
+        <v>16</v>
+      </c>
+      <c r="I68" t="n">
+        <v>12</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="n">
+        <v>0.717</v>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="n">
+        <v>329</v>
+      </c>
+      <c r="O68" t="n">
+        <v>379</v>
+      </c>
+      <c r="P68" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>M-41-HRL</t>
+        </is>
+      </c>
+      <c r="R68" t="n">
+        <v>871</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>Replace n_wells_producing_at_spud with flag_pre_1993</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-04-26T00:23:17.836752</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>8.7</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>flag_flag_post_2000_depleted_replace_n_wells_producing_at_spud</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Cox</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>flag_post_2000_depleted, spud_year, field_cum_gas_at_spud, gas_rate_cv_yr12, peak_gas_rate</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>5</v>
+      </c>
+      <c r="H69" t="n">
+        <v>16</v>
+      </c>
+      <c r="I69" t="n">
+        <v>12</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="n">
+        <v>0.745</v>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="n">
+        <v>284</v>
+      </c>
+      <c r="O69" t="n">
+        <v>379</v>
+      </c>
+      <c r="P69" t="n">
+        <v>95</v>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>M-11-HRL</t>
+        </is>
+      </c>
+      <c r="R69" t="n">
+        <v>791</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>Replace n_wells_producing_at_spud with flag_post_2000_depleted</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-04-26T00:23:18.034956</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>8.7</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>compressed_2f</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Cox</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>n_wells_producing_at_spud, dist_to_gwc_m</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>2</v>
+      </c>
+      <c r="H70" t="n">
+        <v>16</v>
+      </c>
+      <c r="I70" t="n">
+        <v>12</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="n">
+        <v>0.769</v>
+      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="n">
+        <v>329</v>
+      </c>
+      <c r="O70" t="n">
+        <v>379</v>
+      </c>
+      <c r="P70" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>M-11-HRL</t>
+        </is>
+      </c>
+      <c r="R70" t="n">
+        <v>791</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>Field-state + rock-physics compressed</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-04-26T00:32:10.224813</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>8.8</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>intervals_all_wells</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Cox PH</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>n_wells_producing_at_spud, spud_year, field_cum_gas_at_spud, gas_rate_cv_yr12, peak_gas_rate</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>5</v>
+      </c>
+      <c r="H71" t="n">
+        <v>16</v>
+      </c>
+      <c r="I71" t="n">
+        <v>12</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="n">
+        <v>0.788</v>
+      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="n">
+        <v>294</v>
+      </c>
+      <c r="O71" t="n">
+        <v>379</v>
+      </c>
+      <c r="P71" t="n">
+        <v>85</v>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>M-11-HRL</t>
+        </is>
+      </c>
+      <c r="R71" t="n">
+        <v>434</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>Cox PH coverage=8%, 1/12 inside P10-P90</t>
         </is>
       </c>
     </row>
@@ -4492,7 +5434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G892"/>
+  <dimension ref="A1:G1032"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26804,6 +27746,3506 @@
         <v>15</v>
       </c>
       <c r="G892" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="n">
+        <v>57</v>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>M-75-HRL</t>
+        </is>
+      </c>
+      <c r="C893" t="n">
+        <v>1</v>
+      </c>
+      <c r="D893" t="n">
+        <v>127</v>
+      </c>
+      <c r="E893" t="n">
+        <v>45</v>
+      </c>
+      <c r="F893" t="n">
+        <v>82</v>
+      </c>
+      <c r="G893" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="n">
+        <v>57</v>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>M-81-HRL</t>
+        </is>
+      </c>
+      <c r="C894" t="n">
+        <v>1</v>
+      </c>
+      <c r="D894" t="n">
+        <v>57</v>
+      </c>
+      <c r="E894" t="n">
+        <v>45</v>
+      </c>
+      <c r="F894" t="n">
+        <v>12</v>
+      </c>
+      <c r="G894" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="n">
+        <v>57</v>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>M-82-HRL</t>
+        </is>
+      </c>
+      <c r="C895" t="n">
+        <v>1</v>
+      </c>
+      <c r="D895" t="n">
+        <v>48</v>
+      </c>
+      <c r="E895" t="n">
+        <v>45</v>
+      </c>
+      <c r="F895" t="n">
+        <v>3</v>
+      </c>
+      <c r="G895" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="n">
+        <v>57</v>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>M-E-2-HRL</t>
+        </is>
+      </c>
+      <c r="C896" t="n">
+        <v>0</v>
+      </c>
+      <c r="D896" t="n">
+        <v>147</v>
+      </c>
+      <c r="E896" t="n">
+        <v>45</v>
+      </c>
+      <c r="F896" t="n">
+        <v>102</v>
+      </c>
+      <c r="G896" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="n">
+        <v>58</v>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>M-11-HRL</t>
+        </is>
+      </c>
+      <c r="C897" t="n">
+        <v>1</v>
+      </c>
+      <c r="D897" t="n">
+        <v>409</v>
+      </c>
+      <c r="E897" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F897" t="n">
+        <v>791</v>
+      </c>
+      <c r="G897" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="n">
+        <v>58</v>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>M-13-HRL</t>
+        </is>
+      </c>
+      <c r="C898" t="n">
+        <v>0</v>
+      </c>
+      <c r="D898" t="n">
+        <v>562</v>
+      </c>
+      <c r="E898" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F898" t="n">
+        <v>638</v>
+      </c>
+      <c r="G898" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="n">
+        <v>58</v>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>M-22-HRL</t>
+        </is>
+      </c>
+      <c r="C899" t="n">
+        <v>0</v>
+      </c>
+      <c r="D899" t="n">
+        <v>524</v>
+      </c>
+      <c r="E899" t="n">
+        <v>379</v>
+      </c>
+      <c r="F899" t="n">
+        <v>145</v>
+      </c>
+      <c r="G899" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="n">
+        <v>58</v>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>M-41-HRL</t>
+        </is>
+      </c>
+      <c r="C900" t="n">
+        <v>1</v>
+      </c>
+      <c r="D900" t="n">
+        <v>329</v>
+      </c>
+      <c r="E900" t="n">
+        <v>409</v>
+      </c>
+      <c r="F900" t="n">
+        <v>80</v>
+      </c>
+      <c r="G900" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="n">
+        <v>58</v>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>M-50-HRL</t>
+        </is>
+      </c>
+      <c r="C901" t="n">
+        <v>1</v>
+      </c>
+      <c r="D901" t="n">
+        <v>379</v>
+      </c>
+      <c r="E901" t="n">
+        <v>299</v>
+      </c>
+      <c r="F901" t="n">
+        <v>80</v>
+      </c>
+      <c r="G901" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="n">
+        <v>59</v>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>M-56-HRL</t>
+        </is>
+      </c>
+      <c r="C902" t="n">
+        <v>1</v>
+      </c>
+      <c r="D902" t="n">
+        <v>299</v>
+      </c>
+      <c r="E902" t="n">
+        <v>259</v>
+      </c>
+      <c r="F902" t="n">
+        <v>40</v>
+      </c>
+      <c r="G902" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="n">
+        <v>59</v>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>M-57-HRL</t>
+        </is>
+      </c>
+      <c r="C903" t="n">
+        <v>0</v>
+      </c>
+      <c r="D903" t="n">
+        <v>383</v>
+      </c>
+      <c r="E903" t="n">
+        <v>329</v>
+      </c>
+      <c r="F903" t="n">
+        <v>54</v>
+      </c>
+      <c r="G903" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="n">
+        <v>59</v>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>M-58-HRL</t>
+        </is>
+      </c>
+      <c r="C904" t="n">
+        <v>1</v>
+      </c>
+      <c r="D904" t="n">
+        <v>88</v>
+      </c>
+      <c r="E904" t="n">
+        <v>275</v>
+      </c>
+      <c r="F904" t="n">
+        <v>187</v>
+      </c>
+      <c r="G904" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="n">
+        <v>59</v>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>M-61-HRL</t>
+        </is>
+      </c>
+      <c r="C905" t="n">
+        <v>1</v>
+      </c>
+      <c r="D905" t="n">
+        <v>284</v>
+      </c>
+      <c r="E905" t="n">
+        <v>329</v>
+      </c>
+      <c r="F905" t="n">
+        <v>45</v>
+      </c>
+      <c r="G905" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="n">
+        <v>59</v>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>M-63-HRL</t>
+        </is>
+      </c>
+      <c r="C906" t="n">
+        <v>1</v>
+      </c>
+      <c r="D906" t="n">
+        <v>275</v>
+      </c>
+      <c r="E906" t="n">
+        <v>284</v>
+      </c>
+      <c r="F906" t="n">
+        <v>9</v>
+      </c>
+      <c r="G906" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="n">
+        <v>59</v>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>M-65-HRL</t>
+        </is>
+      </c>
+      <c r="C907" t="n">
+        <v>1</v>
+      </c>
+      <c r="D907" t="n">
+        <v>259</v>
+      </c>
+      <c r="E907" t="n">
+        <v>284</v>
+      </c>
+      <c r="F907" t="n">
+        <v>25</v>
+      </c>
+      <c r="G907" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="n">
+        <v>59</v>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>M-67-HRL</t>
+        </is>
+      </c>
+      <c r="C908" t="n">
+        <v>1</v>
+      </c>
+      <c r="D908" t="n">
+        <v>45</v>
+      </c>
+      <c r="E908" t="n">
+        <v>259</v>
+      </c>
+      <c r="F908" t="n">
+        <v>214</v>
+      </c>
+      <c r="G908" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="n">
+        <v>60</v>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>M-75-HRL</t>
+        </is>
+      </c>
+      <c r="C909" t="n">
+        <v>1</v>
+      </c>
+      <c r="D909" t="n">
+        <v>127</v>
+      </c>
+      <c r="E909" t="n">
+        <v>57</v>
+      </c>
+      <c r="F909" t="n">
+        <v>70</v>
+      </c>
+      <c r="G909" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="n">
+        <v>60</v>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>M-81-HRL</t>
+        </is>
+      </c>
+      <c r="C910" t="n">
+        <v>1</v>
+      </c>
+      <c r="D910" t="n">
+        <v>57</v>
+      </c>
+      <c r="E910" t="n">
+        <v>88</v>
+      </c>
+      <c r="F910" t="n">
+        <v>31</v>
+      </c>
+      <c r="G910" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="n">
+        <v>60</v>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>M-82-HRL</t>
+        </is>
+      </c>
+      <c r="C911" t="n">
+        <v>1</v>
+      </c>
+      <c r="D911" t="n">
+        <v>48</v>
+      </c>
+      <c r="E911" t="n">
+        <v>127</v>
+      </c>
+      <c r="F911" t="n">
+        <v>79</v>
+      </c>
+      <c r="G911" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="n">
+        <v>60</v>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>M-E-2-HRL</t>
+        </is>
+      </c>
+      <c r="C912" t="n">
+        <v>0</v>
+      </c>
+      <c r="D912" t="n">
+        <v>147</v>
+      </c>
+      <c r="E912" t="n">
+        <v>57</v>
+      </c>
+      <c r="F912" t="n">
+        <v>90</v>
+      </c>
+      <c r="G912" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="n">
+        <v>61</v>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>M-11-HRL</t>
+        </is>
+      </c>
+      <c r="C913" t="n">
+        <v>1</v>
+      </c>
+      <c r="D913" t="n">
+        <v>409</v>
+      </c>
+      <c r="E913" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F913" t="n">
+        <v>791</v>
+      </c>
+      <c r="G913" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="n">
+        <v>61</v>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>M-13-HRL</t>
+        </is>
+      </c>
+      <c r="C914" t="n">
+        <v>0</v>
+      </c>
+      <c r="D914" t="n">
+        <v>562</v>
+      </c>
+      <c r="E914" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F914" t="n">
+        <v>638</v>
+      </c>
+      <c r="G914" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="n">
+        <v>61</v>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>M-22-HRL</t>
+        </is>
+      </c>
+      <c r="C915" t="n">
+        <v>0</v>
+      </c>
+      <c r="D915" t="n">
+        <v>524</v>
+      </c>
+      <c r="E915" t="n">
+        <v>409</v>
+      </c>
+      <c r="F915" t="n">
+        <v>115</v>
+      </c>
+      <c r="G915" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="n">
+        <v>61</v>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>M-41-HRL</t>
+        </is>
+      </c>
+      <c r="C916" t="n">
+        <v>1</v>
+      </c>
+      <c r="D916" t="n">
+        <v>329</v>
+      </c>
+      <c r="E916" t="n">
+        <v>409</v>
+      </c>
+      <c r="F916" t="n">
+        <v>80</v>
+      </c>
+      <c r="G916" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="n">
+        <v>61</v>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>M-50-HRL</t>
+        </is>
+      </c>
+      <c r="C917" t="n">
+        <v>1</v>
+      </c>
+      <c r="D917" t="n">
+        <v>379</v>
+      </c>
+      <c r="E917" t="n">
+        <v>329</v>
+      </c>
+      <c r="F917" t="n">
+        <v>50</v>
+      </c>
+      <c r="G917" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="n">
+        <v>61</v>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>M-56-HRL</t>
+        </is>
+      </c>
+      <c r="C918" t="n">
+        <v>1</v>
+      </c>
+      <c r="D918" t="n">
+        <v>299</v>
+      </c>
+      <c r="E918" t="n">
+        <v>275</v>
+      </c>
+      <c r="F918" t="n">
+        <v>24</v>
+      </c>
+      <c r="G918" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="n">
+        <v>61</v>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>M-57-HRL</t>
+        </is>
+      </c>
+      <c r="C919" t="n">
+        <v>0</v>
+      </c>
+      <c r="D919" t="n">
+        <v>383</v>
+      </c>
+      <c r="E919" t="n">
+        <v>284</v>
+      </c>
+      <c r="F919" t="n">
+        <v>99</v>
+      </c>
+      <c r="G919" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="n">
+        <v>61</v>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>M-61-HRL</t>
+        </is>
+      </c>
+      <c r="C920" t="n">
+        <v>1</v>
+      </c>
+      <c r="D920" t="n">
+        <v>284</v>
+      </c>
+      <c r="E920" t="n">
+        <v>329</v>
+      </c>
+      <c r="F920" t="n">
+        <v>45</v>
+      </c>
+      <c r="G920" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="n">
+        <v>61</v>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>M-63-HRL</t>
+        </is>
+      </c>
+      <c r="C921" t="n">
+        <v>1</v>
+      </c>
+      <c r="D921" t="n">
+        <v>275</v>
+      </c>
+      <c r="E921" t="n">
+        <v>284</v>
+      </c>
+      <c r="F921" t="n">
+        <v>9</v>
+      </c>
+      <c r="G921" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="n">
+        <v>61</v>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>M-65-HRL</t>
+        </is>
+      </c>
+      <c r="C922" t="n">
+        <v>1</v>
+      </c>
+      <c r="D922" t="n">
+        <v>259</v>
+      </c>
+      <c r="E922" t="n">
+        <v>284</v>
+      </c>
+      <c r="F922" t="n">
+        <v>25</v>
+      </c>
+      <c r="G922" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="n">
+        <v>61</v>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>M-75-HRL</t>
+        </is>
+      </c>
+      <c r="C923" t="n">
+        <v>1</v>
+      </c>
+      <c r="D923" t="n">
+        <v>127</v>
+      </c>
+      <c r="E923" t="n">
+        <v>259</v>
+      </c>
+      <c r="F923" t="n">
+        <v>132</v>
+      </c>
+      <c r="G923" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="n">
+        <v>61</v>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>M-E-2-HRL</t>
+        </is>
+      </c>
+      <c r="C924" t="n">
+        <v>0</v>
+      </c>
+      <c r="D924" t="n">
+        <v>147</v>
+      </c>
+      <c r="E924" t="n">
+        <v>127</v>
+      </c>
+      <c r="F924" t="n">
+        <v>20</v>
+      </c>
+      <c r="G924" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="n">
+        <v>62</v>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>M-58-HRL</t>
+        </is>
+      </c>
+      <c r="C925" t="n">
+        <v>1</v>
+      </c>
+      <c r="D925" t="n">
+        <v>88</v>
+      </c>
+      <c r="E925" t="n">
+        <v>284</v>
+      </c>
+      <c r="F925" t="n">
+        <v>196</v>
+      </c>
+      <c r="G925" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="n">
+        <v>62</v>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>M-67-HRL</t>
+        </is>
+      </c>
+      <c r="C926" t="n">
+        <v>1</v>
+      </c>
+      <c r="D926" t="n">
+        <v>45</v>
+      </c>
+      <c r="E926" t="n">
+        <v>275</v>
+      </c>
+      <c r="F926" t="n">
+        <v>230</v>
+      </c>
+      <c r="G926" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="n">
+        <v>62</v>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>M-81-HRL</t>
+        </is>
+      </c>
+      <c r="C927" t="n">
+        <v>1</v>
+      </c>
+      <c r="D927" t="n">
+        <v>57</v>
+      </c>
+      <c r="E927" t="n">
+        <v>259</v>
+      </c>
+      <c r="F927" t="n">
+        <v>202</v>
+      </c>
+      <c r="G927" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="n">
+        <v>62</v>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>M-82-HRL</t>
+        </is>
+      </c>
+      <c r="C928" t="n">
+        <v>1</v>
+      </c>
+      <c r="D928" t="n">
+        <v>48</v>
+      </c>
+      <c r="E928" t="n">
+        <v>259</v>
+      </c>
+      <c r="F928" t="n">
+        <v>211</v>
+      </c>
+      <c r="G928" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="n">
+        <v>63</v>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>M-11-HRL</t>
+        </is>
+      </c>
+      <c r="C929" t="n">
+        <v>1</v>
+      </c>
+      <c r="D929" t="n">
+        <v>409</v>
+      </c>
+      <c r="E929" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F929" t="n">
+        <v>791</v>
+      </c>
+      <c r="G929" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="n">
+        <v>63</v>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>M-13-HRL</t>
+        </is>
+      </c>
+      <c r="C930" t="n">
+        <v>0</v>
+      </c>
+      <c r="D930" t="n">
+        <v>562</v>
+      </c>
+      <c r="E930" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F930" t="n">
+        <v>638</v>
+      </c>
+      <c r="G930" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="n">
+        <v>63</v>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>M-81-HRL</t>
+        </is>
+      </c>
+      <c r="C931" t="n">
+        <v>1</v>
+      </c>
+      <c r="D931" t="n">
+        <v>57</v>
+      </c>
+      <c r="E931" t="n">
+        <v>48</v>
+      </c>
+      <c r="F931" t="n">
+        <v>9</v>
+      </c>
+      <c r="G931" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="n">
+        <v>63</v>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>M-E-2-HRL</t>
+        </is>
+      </c>
+      <c r="C932" t="n">
+        <v>0</v>
+      </c>
+      <c r="D932" t="n">
+        <v>147</v>
+      </c>
+      <c r="E932" t="n">
+        <v>88</v>
+      </c>
+      <c r="F932" t="n">
+        <v>59</v>
+      </c>
+      <c r="G932" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="n">
+        <v>64</v>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>M-11-HRL</t>
+        </is>
+      </c>
+      <c r="C933" t="n">
+        <v>1</v>
+      </c>
+      <c r="D933" t="n">
+        <v>409</v>
+      </c>
+      <c r="E933" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F933" t="n">
+        <v>791</v>
+      </c>
+      <c r="G933" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="n">
+        <v>64</v>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>M-13-HRL</t>
+        </is>
+      </c>
+      <c r="C934" t="n">
+        <v>0</v>
+      </c>
+      <c r="D934" t="n">
+        <v>562</v>
+      </c>
+      <c r="E934" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F934" t="n">
+        <v>638</v>
+      </c>
+      <c r="G934" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="n">
+        <v>64</v>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>M-22-HRL</t>
+        </is>
+      </c>
+      <c r="C935" t="n">
+        <v>0</v>
+      </c>
+      <c r="D935" t="n">
+        <v>524</v>
+      </c>
+      <c r="E935" t="n">
+        <v>379</v>
+      </c>
+      <c r="F935" t="n">
+        <v>145</v>
+      </c>
+      <c r="G935" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="n">
+        <v>64</v>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>M-41-HRL</t>
+        </is>
+      </c>
+      <c r="C936" t="n">
+        <v>1</v>
+      </c>
+      <c r="D936" t="n">
+        <v>329</v>
+      </c>
+      <c r="E936" t="n">
+        <v>409</v>
+      </c>
+      <c r="F936" t="n">
+        <v>80</v>
+      </c>
+      <c r="G936" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="n">
+        <v>64</v>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>M-50-HRL</t>
+        </is>
+      </c>
+      <c r="C937" t="n">
+        <v>1</v>
+      </c>
+      <c r="D937" t="n">
+        <v>379</v>
+      </c>
+      <c r="E937" t="n">
+        <v>299</v>
+      </c>
+      <c r="F937" t="n">
+        <v>80</v>
+      </c>
+      <c r="G937" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="n">
+        <v>64</v>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>M-56-HRL</t>
+        </is>
+      </c>
+      <c r="C938" t="n">
+        <v>1</v>
+      </c>
+      <c r="D938" t="n">
+        <v>299</v>
+      </c>
+      <c r="E938" t="n">
+        <v>259</v>
+      </c>
+      <c r="F938" t="n">
+        <v>40</v>
+      </c>
+      <c r="G938" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="n">
+        <v>64</v>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>M-57-HRL</t>
+        </is>
+      </c>
+      <c r="C939" t="n">
+        <v>0</v>
+      </c>
+      <c r="D939" t="n">
+        <v>383</v>
+      </c>
+      <c r="E939" t="n">
+        <v>329</v>
+      </c>
+      <c r="F939" t="n">
+        <v>54</v>
+      </c>
+      <c r="G939" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="n">
+        <v>64</v>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>M-58-HRL</t>
+        </is>
+      </c>
+      <c r="C940" t="n">
+        <v>1</v>
+      </c>
+      <c r="D940" t="n">
+        <v>88</v>
+      </c>
+      <c r="E940" t="n">
+        <v>275</v>
+      </c>
+      <c r="F940" t="n">
+        <v>187</v>
+      </c>
+      <c r="G940" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="n">
+        <v>64</v>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>M-61-HRL</t>
+        </is>
+      </c>
+      <c r="C941" t="n">
+        <v>1</v>
+      </c>
+      <c r="D941" t="n">
+        <v>284</v>
+      </c>
+      <c r="E941" t="n">
+        <v>329</v>
+      </c>
+      <c r="F941" t="n">
+        <v>45</v>
+      </c>
+      <c r="G941" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="n">
+        <v>64</v>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>M-63-HRL</t>
+        </is>
+      </c>
+      <c r="C942" t="n">
+        <v>1</v>
+      </c>
+      <c r="D942" t="n">
+        <v>275</v>
+      </c>
+      <c r="E942" t="n">
+        <v>284</v>
+      </c>
+      <c r="F942" t="n">
+        <v>9</v>
+      </c>
+      <c r="G942" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="n">
+        <v>64</v>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>M-65-HRL</t>
+        </is>
+      </c>
+      <c r="C943" t="n">
+        <v>1</v>
+      </c>
+      <c r="D943" t="n">
+        <v>259</v>
+      </c>
+      <c r="E943" t="n">
+        <v>284</v>
+      </c>
+      <c r="F943" t="n">
+        <v>25</v>
+      </c>
+      <c r="G943" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="n">
+        <v>64</v>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>M-67-HRL</t>
+        </is>
+      </c>
+      <c r="C944" t="n">
+        <v>1</v>
+      </c>
+      <c r="D944" t="n">
+        <v>45</v>
+      </c>
+      <c r="E944" t="n">
+        <v>259</v>
+      </c>
+      <c r="F944" t="n">
+        <v>214</v>
+      </c>
+      <c r="G944" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="n">
+        <v>64</v>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>M-75-HRL</t>
+        </is>
+      </c>
+      <c r="C945" t="n">
+        <v>1</v>
+      </c>
+      <c r="D945" t="n">
+        <v>127</v>
+      </c>
+      <c r="E945" t="n">
+        <v>57</v>
+      </c>
+      <c r="F945" t="n">
+        <v>70</v>
+      </c>
+      <c r="G945" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="n">
+        <v>64</v>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>M-81-HRL</t>
+        </is>
+      </c>
+      <c r="C946" t="n">
+        <v>1</v>
+      </c>
+      <c r="D946" t="n">
+        <v>57</v>
+      </c>
+      <c r="E946" t="n">
+        <v>88</v>
+      </c>
+      <c r="F946" t="n">
+        <v>31</v>
+      </c>
+      <c r="G946" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="n">
+        <v>64</v>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>M-82-HRL</t>
+        </is>
+      </c>
+      <c r="C947" t="n">
+        <v>1</v>
+      </c>
+      <c r="D947" t="n">
+        <v>48</v>
+      </c>
+      <c r="E947" t="n">
+        <v>127</v>
+      </c>
+      <c r="F947" t="n">
+        <v>79</v>
+      </c>
+      <c r="G947" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="n">
+        <v>64</v>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>M-E-2-HRL</t>
+        </is>
+      </c>
+      <c r="C948" t="n">
+        <v>0</v>
+      </c>
+      <c r="D948" t="n">
+        <v>147</v>
+      </c>
+      <c r="E948" t="n">
+        <v>57</v>
+      </c>
+      <c r="F948" t="n">
+        <v>90</v>
+      </c>
+      <c r="G948" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="n">
+        <v>65</v>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>M-11-HRL</t>
+        </is>
+      </c>
+      <c r="C949" t="n">
+        <v>1</v>
+      </c>
+      <c r="D949" t="n">
+        <v>409</v>
+      </c>
+      <c r="E949" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F949" t="n">
+        <v>791</v>
+      </c>
+      <c r="G949" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="n">
+        <v>65</v>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>M-13-HRL</t>
+        </is>
+      </c>
+      <c r="C950" t="n">
+        <v>0</v>
+      </c>
+      <c r="D950" t="n">
+        <v>562</v>
+      </c>
+      <c r="E950" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F950" t="n">
+        <v>638</v>
+      </c>
+      <c r="G950" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="n">
+        <v>65</v>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>M-22-HRL</t>
+        </is>
+      </c>
+      <c r="C951" t="n">
+        <v>0</v>
+      </c>
+      <c r="D951" t="n">
+        <v>524</v>
+      </c>
+      <c r="E951" t="n">
+        <v>379</v>
+      </c>
+      <c r="F951" t="n">
+        <v>145</v>
+      </c>
+      <c r="G951" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="n">
+        <v>65</v>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>M-41-HRL</t>
+        </is>
+      </c>
+      <c r="C952" t="n">
+        <v>1</v>
+      </c>
+      <c r="D952" t="n">
+        <v>329</v>
+      </c>
+      <c r="E952" t="n">
+        <v>409</v>
+      </c>
+      <c r="F952" t="n">
+        <v>80</v>
+      </c>
+      <c r="G952" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="n">
+        <v>65</v>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>M-50-HRL</t>
+        </is>
+      </c>
+      <c r="C953" t="n">
+        <v>1</v>
+      </c>
+      <c r="D953" t="n">
+        <v>379</v>
+      </c>
+      <c r="E953" t="n">
+        <v>299</v>
+      </c>
+      <c r="F953" t="n">
+        <v>80</v>
+      </c>
+      <c r="G953" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="n">
+        <v>65</v>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>M-56-HRL</t>
+        </is>
+      </c>
+      <c r="C954" t="n">
+        <v>1</v>
+      </c>
+      <c r="D954" t="n">
+        <v>299</v>
+      </c>
+      <c r="E954" t="n">
+        <v>259</v>
+      </c>
+      <c r="F954" t="n">
+        <v>40</v>
+      </c>
+      <c r="G954" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="n">
+        <v>65</v>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>M-57-HRL</t>
+        </is>
+      </c>
+      <c r="C955" t="n">
+        <v>0</v>
+      </c>
+      <c r="D955" t="n">
+        <v>383</v>
+      </c>
+      <c r="E955" t="n">
+        <v>329</v>
+      </c>
+      <c r="F955" t="n">
+        <v>54</v>
+      </c>
+      <c r="G955" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="n">
+        <v>65</v>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>M-58-HRL</t>
+        </is>
+      </c>
+      <c r="C956" t="n">
+        <v>1</v>
+      </c>
+      <c r="D956" t="n">
+        <v>88</v>
+      </c>
+      <c r="E956" t="n">
+        <v>275</v>
+      </c>
+      <c r="F956" t="n">
+        <v>187</v>
+      </c>
+      <c r="G956" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="n">
+        <v>65</v>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>M-61-HRL</t>
+        </is>
+      </c>
+      <c r="C957" t="n">
+        <v>1</v>
+      </c>
+      <c r="D957" t="n">
+        <v>284</v>
+      </c>
+      <c r="E957" t="n">
+        <v>329</v>
+      </c>
+      <c r="F957" t="n">
+        <v>45</v>
+      </c>
+      <c r="G957" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="n">
+        <v>65</v>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>M-63-HRL</t>
+        </is>
+      </c>
+      <c r="C958" t="n">
+        <v>1</v>
+      </c>
+      <c r="D958" t="n">
+        <v>275</v>
+      </c>
+      <c r="E958" t="n">
+        <v>284</v>
+      </c>
+      <c r="F958" t="n">
+        <v>9</v>
+      </c>
+      <c r="G958" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="n">
+        <v>65</v>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>M-65-HRL</t>
+        </is>
+      </c>
+      <c r="C959" t="n">
+        <v>1</v>
+      </c>
+      <c r="D959" t="n">
+        <v>259</v>
+      </c>
+      <c r="E959" t="n">
+        <v>284</v>
+      </c>
+      <c r="F959" t="n">
+        <v>25</v>
+      </c>
+      <c r="G959" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="n">
+        <v>65</v>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>M-67-HRL</t>
+        </is>
+      </c>
+      <c r="C960" t="n">
+        <v>1</v>
+      </c>
+      <c r="D960" t="n">
+        <v>45</v>
+      </c>
+      <c r="E960" t="n">
+        <v>259</v>
+      </c>
+      <c r="F960" t="n">
+        <v>214</v>
+      </c>
+      <c r="G960" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="n">
+        <v>65</v>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>M-75-HRL</t>
+        </is>
+      </c>
+      <c r="C961" t="n">
+        <v>1</v>
+      </c>
+      <c r="D961" t="n">
+        <v>127</v>
+      </c>
+      <c r="E961" t="n">
+        <v>57</v>
+      </c>
+      <c r="F961" t="n">
+        <v>70</v>
+      </c>
+      <c r="G961" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="n">
+        <v>65</v>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>M-81-HRL</t>
+        </is>
+      </c>
+      <c r="C962" t="n">
+        <v>1</v>
+      </c>
+      <c r="D962" t="n">
+        <v>57</v>
+      </c>
+      <c r="E962" t="n">
+        <v>88</v>
+      </c>
+      <c r="F962" t="n">
+        <v>31</v>
+      </c>
+      <c r="G962" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="n">
+        <v>65</v>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>M-82-HRL</t>
+        </is>
+      </c>
+      <c r="C963" t="n">
+        <v>1</v>
+      </c>
+      <c r="D963" t="n">
+        <v>48</v>
+      </c>
+      <c r="E963" t="n">
+        <v>127</v>
+      </c>
+      <c r="F963" t="n">
+        <v>79</v>
+      </c>
+      <c r="G963" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="n">
+        <v>65</v>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>M-E-2-HRL</t>
+        </is>
+      </c>
+      <c r="C964" t="n">
+        <v>0</v>
+      </c>
+      <c r="D964" t="n">
+        <v>147</v>
+      </c>
+      <c r="E964" t="n">
+        <v>57</v>
+      </c>
+      <c r="F964" t="n">
+        <v>90</v>
+      </c>
+      <c r="G964" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="n">
+        <v>66</v>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>M-75-HRL</t>
+        </is>
+      </c>
+      <c r="C965" t="n">
+        <v>1</v>
+      </c>
+      <c r="D965" t="n">
+        <v>127</v>
+      </c>
+      <c r="E965" t="n">
+        <v>45</v>
+      </c>
+      <c r="F965" t="n">
+        <v>82</v>
+      </c>
+      <c r="G965" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="n">
+        <v>66</v>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>M-81-HRL</t>
+        </is>
+      </c>
+      <c r="C966" t="n">
+        <v>1</v>
+      </c>
+      <c r="D966" t="n">
+        <v>57</v>
+      </c>
+      <c r="E966" t="n">
+        <v>45</v>
+      </c>
+      <c r="F966" t="n">
+        <v>12</v>
+      </c>
+      <c r="G966" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="n">
+        <v>66</v>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>M-82-HRL</t>
+        </is>
+      </c>
+      <c r="C967" t="n">
+        <v>1</v>
+      </c>
+      <c r="D967" t="n">
+        <v>48</v>
+      </c>
+      <c r="E967" t="n">
+        <v>45</v>
+      </c>
+      <c r="F967" t="n">
+        <v>3</v>
+      </c>
+      <c r="G967" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="n">
+        <v>66</v>
+      </c>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t>M-E-2-HRL</t>
+        </is>
+      </c>
+      <c r="C968" t="n">
+        <v>0</v>
+      </c>
+      <c r="D968" t="n">
+        <v>147</v>
+      </c>
+      <c r="E968" t="n">
+        <v>45</v>
+      </c>
+      <c r="F968" t="n">
+        <v>102</v>
+      </c>
+      <c r="G968" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="n">
+        <v>67</v>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>M-11-HRL</t>
+        </is>
+      </c>
+      <c r="C969" t="n">
+        <v>1</v>
+      </c>
+      <c r="D969" t="n">
+        <v>409</v>
+      </c>
+      <c r="E969" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F969" t="n">
+        <v>791</v>
+      </c>
+      <c r="G969" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="n">
+        <v>67</v>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>M-13-HRL</t>
+        </is>
+      </c>
+      <c r="C970" t="n">
+        <v>0</v>
+      </c>
+      <c r="D970" t="n">
+        <v>562</v>
+      </c>
+      <c r="E970" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F970" t="n">
+        <v>638</v>
+      </c>
+      <c r="G970" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="n">
+        <v>67</v>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>M-22-HRL</t>
+        </is>
+      </c>
+      <c r="C971" t="n">
+        <v>0</v>
+      </c>
+      <c r="D971" t="n">
+        <v>524</v>
+      </c>
+      <c r="E971" t="n">
+        <v>379</v>
+      </c>
+      <c r="F971" t="n">
+        <v>145</v>
+      </c>
+      <c r="G971" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="n">
+        <v>67</v>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>M-41-HRL</t>
+        </is>
+      </c>
+      <c r="C972" t="n">
+        <v>1</v>
+      </c>
+      <c r="D972" t="n">
+        <v>329</v>
+      </c>
+      <c r="E972" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F972" t="n">
+        <v>871</v>
+      </c>
+      <c r="G972" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="n">
+        <v>67</v>
+      </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>M-50-HRL</t>
+        </is>
+      </c>
+      <c r="C973" t="n">
+        <v>1</v>
+      </c>
+      <c r="D973" t="n">
+        <v>379</v>
+      </c>
+      <c r="E973" t="n">
+        <v>329</v>
+      </c>
+      <c r="F973" t="n">
+        <v>50</v>
+      </c>
+      <c r="G973" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="n">
+        <v>67</v>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>M-56-HRL</t>
+        </is>
+      </c>
+      <c r="C974" t="n">
+        <v>1</v>
+      </c>
+      <c r="D974" t="n">
+        <v>299</v>
+      </c>
+      <c r="E974" t="n">
+        <v>88</v>
+      </c>
+      <c r="F974" t="n">
+        <v>211</v>
+      </c>
+      <c r="G974" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="n">
+        <v>67</v>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>M-57-HRL</t>
+        </is>
+      </c>
+      <c r="C975" t="n">
+        <v>0</v>
+      </c>
+      <c r="D975" t="n">
+        <v>383</v>
+      </c>
+      <c r="E975" t="n">
+        <v>284</v>
+      </c>
+      <c r="F975" t="n">
+        <v>99</v>
+      </c>
+      <c r="G975" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="n">
+        <v>67</v>
+      </c>
+      <c r="B976" t="inlineStr">
+        <is>
+          <t>M-58-HRL</t>
+        </is>
+      </c>
+      <c r="C976" t="n">
+        <v>1</v>
+      </c>
+      <c r="D976" t="n">
+        <v>88</v>
+      </c>
+      <c r="E976" t="n">
+        <v>259</v>
+      </c>
+      <c r="F976" t="n">
+        <v>171</v>
+      </c>
+      <c r="G976" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="n">
+        <v>67</v>
+      </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>M-61-HRL</t>
+        </is>
+      </c>
+      <c r="C977" t="n">
+        <v>1</v>
+      </c>
+      <c r="D977" t="n">
+        <v>284</v>
+      </c>
+      <c r="E977" t="n">
+        <v>299</v>
+      </c>
+      <c r="F977" t="n">
+        <v>15</v>
+      </c>
+      <c r="G977" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="n">
+        <v>67</v>
+      </c>
+      <c r="B978" t="inlineStr">
+        <is>
+          <t>M-63-HRL</t>
+        </is>
+      </c>
+      <c r="C978" t="n">
+        <v>1</v>
+      </c>
+      <c r="D978" t="n">
+        <v>275</v>
+      </c>
+      <c r="E978" t="n">
+        <v>284</v>
+      </c>
+      <c r="F978" t="n">
+        <v>9</v>
+      </c>
+      <c r="G978" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="n">
+        <v>67</v>
+      </c>
+      <c r="B979" t="inlineStr">
+        <is>
+          <t>M-65-HRL</t>
+        </is>
+      </c>
+      <c r="C979" t="n">
+        <v>1</v>
+      </c>
+      <c r="D979" t="n">
+        <v>259</v>
+      </c>
+      <c r="E979" t="n">
+        <v>299</v>
+      </c>
+      <c r="F979" t="n">
+        <v>40</v>
+      </c>
+      <c r="G979" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="n">
+        <v>67</v>
+      </c>
+      <c r="B980" t="inlineStr">
+        <is>
+          <t>M-67-HRL</t>
+        </is>
+      </c>
+      <c r="C980" t="n">
+        <v>1</v>
+      </c>
+      <c r="D980" t="n">
+        <v>45</v>
+      </c>
+      <c r="E980" t="n">
+        <v>259</v>
+      </c>
+      <c r="F980" t="n">
+        <v>214</v>
+      </c>
+      <c r="G980" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="n">
+        <v>67</v>
+      </c>
+      <c r="B981" t="inlineStr">
+        <is>
+          <t>M-75-HRL</t>
+        </is>
+      </c>
+      <c r="C981" t="n">
+        <v>1</v>
+      </c>
+      <c r="D981" t="n">
+        <v>127</v>
+      </c>
+      <c r="E981" t="n">
+        <v>88</v>
+      </c>
+      <c r="F981" t="n">
+        <v>39</v>
+      </c>
+      <c r="G981" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="n">
+        <v>67</v>
+      </c>
+      <c r="B982" t="inlineStr">
+        <is>
+          <t>M-81-HRL</t>
+        </is>
+      </c>
+      <c r="C982" t="n">
+        <v>1</v>
+      </c>
+      <c r="D982" t="n">
+        <v>57</v>
+      </c>
+      <c r="E982" t="n">
+        <v>127</v>
+      </c>
+      <c r="F982" t="n">
+        <v>70</v>
+      </c>
+      <c r="G982" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="n">
+        <v>67</v>
+      </c>
+      <c r="B983" t="inlineStr">
+        <is>
+          <t>M-82-HRL</t>
+        </is>
+      </c>
+      <c r="C983" t="n">
+        <v>1</v>
+      </c>
+      <c r="D983" t="n">
+        <v>48</v>
+      </c>
+      <c r="E983" t="n">
+        <v>127</v>
+      </c>
+      <c r="F983" t="n">
+        <v>79</v>
+      </c>
+      <c r="G983" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="n">
+        <v>67</v>
+      </c>
+      <c r="B984" t="inlineStr">
+        <is>
+          <t>M-E-2-HRL</t>
+        </is>
+      </c>
+      <c r="C984" t="n">
+        <v>0</v>
+      </c>
+      <c r="D984" t="n">
+        <v>147</v>
+      </c>
+      <c r="E984" t="n">
+        <v>48</v>
+      </c>
+      <c r="F984" t="n">
+        <v>99</v>
+      </c>
+      <c r="G984" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="n">
+        <v>68</v>
+      </c>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>M-11-HRL</t>
+        </is>
+      </c>
+      <c r="C985" t="n">
+        <v>1</v>
+      </c>
+      <c r="D985" t="n">
+        <v>409</v>
+      </c>
+      <c r="E985" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F985" t="n">
+        <v>791</v>
+      </c>
+      <c r="G985" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="n">
+        <v>68</v>
+      </c>
+      <c r="B986" t="inlineStr">
+        <is>
+          <t>M-13-HRL</t>
+        </is>
+      </c>
+      <c r="C986" t="n">
+        <v>0</v>
+      </c>
+      <c r="D986" t="n">
+        <v>562</v>
+      </c>
+      <c r="E986" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F986" t="n">
+        <v>638</v>
+      </c>
+      <c r="G986" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="n">
+        <v>68</v>
+      </c>
+      <c r="B987" t="inlineStr">
+        <is>
+          <t>M-22-HRL</t>
+        </is>
+      </c>
+      <c r="C987" t="n">
+        <v>0</v>
+      </c>
+      <c r="D987" t="n">
+        <v>524</v>
+      </c>
+      <c r="E987" t="n">
+        <v>329</v>
+      </c>
+      <c r="F987" t="n">
+        <v>195</v>
+      </c>
+      <c r="G987" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="n">
+        <v>68</v>
+      </c>
+      <c r="B988" t="inlineStr">
+        <is>
+          <t>M-41-HRL</t>
+        </is>
+      </c>
+      <c r="C988" t="n">
+        <v>1</v>
+      </c>
+      <c r="D988" t="n">
+        <v>329</v>
+      </c>
+      <c r="E988" t="n">
+        <v>409</v>
+      </c>
+      <c r="F988" t="n">
+        <v>80</v>
+      </c>
+      <c r="G988" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="n">
+        <v>68</v>
+      </c>
+      <c r="B989" t="inlineStr">
+        <is>
+          <t>M-50-HRL</t>
+        </is>
+      </c>
+      <c r="C989" t="n">
+        <v>1</v>
+      </c>
+      <c r="D989" t="n">
+        <v>379</v>
+      </c>
+      <c r="E989" t="n">
+        <v>284</v>
+      </c>
+      <c r="F989" t="n">
+        <v>95</v>
+      </c>
+      <c r="G989" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="n">
+        <v>68</v>
+      </c>
+      <c r="B990" t="inlineStr">
+        <is>
+          <t>M-56-HRL</t>
+        </is>
+      </c>
+      <c r="C990" t="n">
+        <v>1</v>
+      </c>
+      <c r="D990" t="n">
+        <v>299</v>
+      </c>
+      <c r="E990" t="n">
+        <v>127</v>
+      </c>
+      <c r="F990" t="n">
+        <v>172</v>
+      </c>
+      <c r="G990" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="n">
+        <v>68</v>
+      </c>
+      <c r="B991" t="inlineStr">
+        <is>
+          <t>M-57-HRL</t>
+        </is>
+      </c>
+      <c r="C991" t="n">
+        <v>0</v>
+      </c>
+      <c r="D991" t="n">
+        <v>383</v>
+      </c>
+      <c r="E991" t="n">
+        <v>329</v>
+      </c>
+      <c r="F991" t="n">
+        <v>54</v>
+      </c>
+      <c r="G991" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="n">
+        <v>68</v>
+      </c>
+      <c r="B992" t="inlineStr">
+        <is>
+          <t>M-58-HRL</t>
+        </is>
+      </c>
+      <c r="C992" t="n">
+        <v>1</v>
+      </c>
+      <c r="D992" t="n">
+        <v>88</v>
+      </c>
+      <c r="E992" t="n">
+        <v>275</v>
+      </c>
+      <c r="F992" t="n">
+        <v>187</v>
+      </c>
+      <c r="G992" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="n">
+        <v>68</v>
+      </c>
+      <c r="B993" t="inlineStr">
+        <is>
+          <t>M-61-HRL</t>
+        </is>
+      </c>
+      <c r="C993" t="n">
+        <v>1</v>
+      </c>
+      <c r="D993" t="n">
+        <v>284</v>
+      </c>
+      <c r="E993" t="n">
+        <v>329</v>
+      </c>
+      <c r="F993" t="n">
+        <v>45</v>
+      </c>
+      <c r="G993" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="n">
+        <v>68</v>
+      </c>
+      <c r="B994" t="inlineStr">
+        <is>
+          <t>M-63-HRL</t>
+        </is>
+      </c>
+      <c r="C994" t="n">
+        <v>1</v>
+      </c>
+      <c r="D994" t="n">
+        <v>275</v>
+      </c>
+      <c r="E994" t="n">
+        <v>284</v>
+      </c>
+      <c r="F994" t="n">
+        <v>9</v>
+      </c>
+      <c r="G994" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="n">
+        <v>68</v>
+      </c>
+      <c r="B995" t="inlineStr">
+        <is>
+          <t>M-65-HRL</t>
+        </is>
+      </c>
+      <c r="C995" t="n">
+        <v>1</v>
+      </c>
+      <c r="D995" t="n">
+        <v>259</v>
+      </c>
+      <c r="E995" t="n">
+        <v>299</v>
+      </c>
+      <c r="F995" t="n">
+        <v>40</v>
+      </c>
+      <c r="G995" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="n">
+        <v>68</v>
+      </c>
+      <c r="B996" t="inlineStr">
+        <is>
+          <t>M-67-HRL</t>
+        </is>
+      </c>
+      <c r="C996" t="n">
+        <v>1</v>
+      </c>
+      <c r="D996" t="n">
+        <v>45</v>
+      </c>
+      <c r="E996" t="n">
+        <v>275</v>
+      </c>
+      <c r="F996" t="n">
+        <v>230</v>
+      </c>
+      <c r="G996" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="n">
+        <v>68</v>
+      </c>
+      <c r="B997" t="inlineStr">
+        <is>
+          <t>M-75-HRL</t>
+        </is>
+      </c>
+      <c r="C997" t="n">
+        <v>1</v>
+      </c>
+      <c r="D997" t="n">
+        <v>127</v>
+      </c>
+      <c r="E997" t="n">
+        <v>88</v>
+      </c>
+      <c r="F997" t="n">
+        <v>39</v>
+      </c>
+      <c r="G997" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="n">
+        <v>68</v>
+      </c>
+      <c r="B998" t="inlineStr">
+        <is>
+          <t>M-81-HRL</t>
+        </is>
+      </c>
+      <c r="C998" t="n">
+        <v>1</v>
+      </c>
+      <c r="D998" t="n">
+        <v>57</v>
+      </c>
+      <c r="E998" t="n">
+        <v>127</v>
+      </c>
+      <c r="F998" t="n">
+        <v>70</v>
+      </c>
+      <c r="G998" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="n">
+        <v>68</v>
+      </c>
+      <c r="B999" t="inlineStr">
+        <is>
+          <t>M-82-HRL</t>
+        </is>
+      </c>
+      <c r="C999" t="n">
+        <v>1</v>
+      </c>
+      <c r="D999" t="n">
+        <v>48</v>
+      </c>
+      <c r="E999" t="n">
+        <v>127</v>
+      </c>
+      <c r="F999" t="n">
+        <v>79</v>
+      </c>
+      <c r="G999" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="n">
+        <v>68</v>
+      </c>
+      <c r="B1000" t="inlineStr">
+        <is>
+          <t>M-E-2-HRL</t>
+        </is>
+      </c>
+      <c r="C1000" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1000" t="n">
+        <v>147</v>
+      </c>
+      <c r="E1000" t="n">
+        <v>48</v>
+      </c>
+      <c r="F1000" t="n">
+        <v>99</v>
+      </c>
+      <c r="G1000" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="n">
+        <v>69</v>
+      </c>
+      <c r="B1001" t="inlineStr">
+        <is>
+          <t>M-11-HRL</t>
+        </is>
+      </c>
+      <c r="C1001" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1001" t="n">
+        <v>409</v>
+      </c>
+      <c r="E1001" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F1001" t="n">
+        <v>791</v>
+      </c>
+      <c r="G1001" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="n">
+        <v>69</v>
+      </c>
+      <c r="B1002" t="inlineStr">
+        <is>
+          <t>M-13-HRL</t>
+        </is>
+      </c>
+      <c r="C1002" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1002" t="n">
+        <v>562</v>
+      </c>
+      <c r="E1002" t="n">
+        <v>409</v>
+      </c>
+      <c r="F1002" t="n">
+        <v>153</v>
+      </c>
+      <c r="G1002" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="n">
+        <v>69</v>
+      </c>
+      <c r="B1003" t="inlineStr">
+        <is>
+          <t>M-22-HRL</t>
+        </is>
+      </c>
+      <c r="C1003" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1003" t="n">
+        <v>524</v>
+      </c>
+      <c r="E1003" t="n">
+        <v>379</v>
+      </c>
+      <c r="F1003" t="n">
+        <v>145</v>
+      </c>
+      <c r="G1003" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="n">
+        <v>69</v>
+      </c>
+      <c r="B1004" t="inlineStr">
+        <is>
+          <t>M-41-HRL</t>
+        </is>
+      </c>
+      <c r="C1004" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1004" t="n">
+        <v>329</v>
+      </c>
+      <c r="E1004" t="n">
+        <v>379</v>
+      </c>
+      <c r="F1004" t="n">
+        <v>50</v>
+      </c>
+      <c r="G1004" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="n">
+        <v>69</v>
+      </c>
+      <c r="B1005" t="inlineStr">
+        <is>
+          <t>M-50-HRL</t>
+        </is>
+      </c>
+      <c r="C1005" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1005" t="n">
+        <v>379</v>
+      </c>
+      <c r="E1005" t="n">
+        <v>329</v>
+      </c>
+      <c r="F1005" t="n">
+        <v>50</v>
+      </c>
+      <c r="G1005" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="n">
+        <v>69</v>
+      </c>
+      <c r="B1006" t="inlineStr">
+        <is>
+          <t>M-56-HRL</t>
+        </is>
+      </c>
+      <c r="C1006" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1006" t="n">
+        <v>299</v>
+      </c>
+      <c r="E1006" t="n">
+        <v>329</v>
+      </c>
+      <c r="F1006" t="n">
+        <v>30</v>
+      </c>
+      <c r="G1006" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="n">
+        <v>69</v>
+      </c>
+      <c r="B1007" t="inlineStr">
+        <is>
+          <t>M-57-HRL</t>
+        </is>
+      </c>
+      <c r="C1007" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1007" t="n">
+        <v>383</v>
+      </c>
+      <c r="E1007" t="n">
+        <v>284</v>
+      </c>
+      <c r="F1007" t="n">
+        <v>99</v>
+      </c>
+      <c r="G1007" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="n">
+        <v>69</v>
+      </c>
+      <c r="B1008" t="inlineStr">
+        <is>
+          <t>M-58-HRL</t>
+        </is>
+      </c>
+      <c r="C1008" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1008" t="n">
+        <v>88</v>
+      </c>
+      <c r="E1008" t="n">
+        <v>299</v>
+      </c>
+      <c r="F1008" t="n">
+        <v>211</v>
+      </c>
+      <c r="G1008" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="n">
+        <v>69</v>
+      </c>
+      <c r="B1009" t="inlineStr">
+        <is>
+          <t>M-61-HRL</t>
+        </is>
+      </c>
+      <c r="C1009" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1009" t="n">
+        <v>284</v>
+      </c>
+      <c r="E1009" t="n">
+        <v>275</v>
+      </c>
+      <c r="F1009" t="n">
+        <v>9</v>
+      </c>
+      <c r="G1009" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="n">
+        <v>69</v>
+      </c>
+      <c r="B1010" t="inlineStr">
+        <is>
+          <t>M-63-HRL</t>
+        </is>
+      </c>
+      <c r="C1010" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1010" t="n">
+        <v>275</v>
+      </c>
+      <c r="E1010" t="n">
+        <v>284</v>
+      </c>
+      <c r="F1010" t="n">
+        <v>9</v>
+      </c>
+      <c r="G1010" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="n">
+        <v>69</v>
+      </c>
+      <c r="B1011" t="inlineStr">
+        <is>
+          <t>M-65-HRL</t>
+        </is>
+      </c>
+      <c r="C1011" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1011" t="n">
+        <v>259</v>
+      </c>
+      <c r="E1011" t="n">
+        <v>275</v>
+      </c>
+      <c r="F1011" t="n">
+        <v>16</v>
+      </c>
+      <c r="G1011" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="n">
+        <v>69</v>
+      </c>
+      <c r="B1012" t="inlineStr">
+        <is>
+          <t>M-67-HRL</t>
+        </is>
+      </c>
+      <c r="C1012" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1012" t="n">
+        <v>45</v>
+      </c>
+      <c r="E1012" t="n">
+        <v>259</v>
+      </c>
+      <c r="F1012" t="n">
+        <v>214</v>
+      </c>
+      <c r="G1012" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="n">
+        <v>69</v>
+      </c>
+      <c r="B1013" t="inlineStr">
+        <is>
+          <t>M-75-HRL</t>
+        </is>
+      </c>
+      <c r="C1013" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1013" t="n">
+        <v>127</v>
+      </c>
+      <c r="E1013" t="n">
+        <v>57</v>
+      </c>
+      <c r="F1013" t="n">
+        <v>70</v>
+      </c>
+      <c r="G1013" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="n">
+        <v>69</v>
+      </c>
+      <c r="B1014" t="inlineStr">
+        <is>
+          <t>M-81-HRL</t>
+        </is>
+      </c>
+      <c r="C1014" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1014" t="n">
+        <v>57</v>
+      </c>
+      <c r="E1014" t="n">
+        <v>127</v>
+      </c>
+      <c r="F1014" t="n">
+        <v>70</v>
+      </c>
+      <c r="G1014" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="n">
+        <v>69</v>
+      </c>
+      <c r="B1015" t="inlineStr">
+        <is>
+          <t>M-82-HRL</t>
+        </is>
+      </c>
+      <c r="C1015" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1015" t="n">
+        <v>48</v>
+      </c>
+      <c r="E1015" t="n">
+        <v>259</v>
+      </c>
+      <c r="F1015" t="n">
+        <v>211</v>
+      </c>
+      <c r="G1015" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="n">
+        <v>69</v>
+      </c>
+      <c r="B1016" t="inlineStr">
+        <is>
+          <t>M-E-2-HRL</t>
+        </is>
+      </c>
+      <c r="C1016" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1016" t="n">
+        <v>147</v>
+      </c>
+      <c r="E1016" t="n">
+        <v>48</v>
+      </c>
+      <c r="F1016" t="n">
+        <v>99</v>
+      </c>
+      <c r="G1016" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="n">
+        <v>70</v>
+      </c>
+      <c r="B1017" t="inlineStr">
+        <is>
+          <t>M-67-HRL</t>
+        </is>
+      </c>
+      <c r="C1017" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1017" t="n">
+        <v>45</v>
+      </c>
+      <c r="E1017" t="n">
+        <v>194.6</v>
+      </c>
+      <c r="F1017" t="n">
+        <v>149.6</v>
+      </c>
+      <c r="G1017" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="n">
+        <v>70</v>
+      </c>
+      <c r="B1018" t="inlineStr">
+        <is>
+          <t>M-82-HRL</t>
+        </is>
+      </c>
+      <c r="C1018" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1018" t="n">
+        <v>48</v>
+      </c>
+      <c r="E1018" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="F1018" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="G1018" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="n">
+        <v>70</v>
+      </c>
+      <c r="B1019" t="inlineStr">
+        <is>
+          <t>M-81-HRL</t>
+        </is>
+      </c>
+      <c r="C1019" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1019" t="n">
+        <v>57</v>
+      </c>
+      <c r="E1019" t="n">
+        <v>57</v>
+      </c>
+      <c r="F1019" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1019" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="n">
+        <v>70</v>
+      </c>
+      <c r="B1020" t="inlineStr">
+        <is>
+          <t>M-58-HRL</t>
+        </is>
+      </c>
+      <c r="C1020" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1020" t="n">
+        <v>88</v>
+      </c>
+      <c r="E1020" t="n">
+        <v>270.7</v>
+      </c>
+      <c r="F1020" t="n">
+        <v>182.7</v>
+      </c>
+      <c r="G1020" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="n">
+        <v>70</v>
+      </c>
+      <c r="B1021" t="inlineStr">
+        <is>
+          <t>M-75-HRL</t>
+        </is>
+      </c>
+      <c r="C1021" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1021" t="n">
+        <v>127</v>
+      </c>
+      <c r="E1021" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="F1021" t="n">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="G1021" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="n">
+        <v>70</v>
+      </c>
+      <c r="B1022" t="inlineStr">
+        <is>
+          <t>M-E-2-HRL</t>
+        </is>
+      </c>
+      <c r="C1022" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1022" t="n">
+        <v>147</v>
+      </c>
+      <c r="E1022" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="F1022" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="G1022" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="n">
+        <v>70</v>
+      </c>
+      <c r="B1023" t="inlineStr">
+        <is>
+          <t>M-65-HRL</t>
+        </is>
+      </c>
+      <c r="C1023" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1023" t="n">
+        <v>259</v>
+      </c>
+      <c r="E1023" t="n">
+        <v>278</v>
+      </c>
+      <c r="F1023" t="n">
+        <v>19</v>
+      </c>
+      <c r="G1023" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="n">
+        <v>70</v>
+      </c>
+      <c r="B1024" t="inlineStr">
+        <is>
+          <t>M-63-HRL</t>
+        </is>
+      </c>
+      <c r="C1024" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1024" t="n">
+        <v>275</v>
+      </c>
+      <c r="E1024" t="n">
+        <v>265.3</v>
+      </c>
+      <c r="F1024" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="G1024" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="n">
+        <v>70</v>
+      </c>
+      <c r="B1025" t="inlineStr">
+        <is>
+          <t>M-61-HRL</t>
+        </is>
+      </c>
+      <c r="C1025" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1025" t="n">
+        <v>284</v>
+      </c>
+      <c r="E1025" t="n">
+        <v>302.7</v>
+      </c>
+      <c r="F1025" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="G1025" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="n">
+        <v>70</v>
+      </c>
+      <c r="B1026" t="inlineStr">
+        <is>
+          <t>M-56-HRL</t>
+        </is>
+      </c>
+      <c r="C1026" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1026" t="n">
+        <v>299</v>
+      </c>
+      <c r="E1026" t="n">
+        <v>180.9</v>
+      </c>
+      <c r="F1026" t="n">
+        <v>118.1</v>
+      </c>
+      <c r="G1026" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="n">
+        <v>70</v>
+      </c>
+      <c r="B1027" t="inlineStr">
+        <is>
+          <t>M-41-HRL</t>
+        </is>
+      </c>
+      <c r="C1027" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1027" t="n">
+        <v>329</v>
+      </c>
+      <c r="E1027" t="n">
+        <v>574.5</v>
+      </c>
+      <c r="F1027" t="n">
+        <v>245.5</v>
+      </c>
+      <c r="G1027" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="n">
+        <v>70</v>
+      </c>
+      <c r="B1028" t="inlineStr">
+        <is>
+          <t>M-50-HRL</t>
+        </is>
+      </c>
+      <c r="C1028" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1028" t="n">
+        <v>379</v>
+      </c>
+      <c r="E1028" t="n">
+        <v>294</v>
+      </c>
+      <c r="F1028" t="n">
+        <v>85</v>
+      </c>
+      <c r="G1028" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="n">
+        <v>70</v>
+      </c>
+      <c r="B1029" t="inlineStr">
+        <is>
+          <t>M-57-HRL</t>
+        </is>
+      </c>
+      <c r="C1029" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1029" t="n">
+        <v>383</v>
+      </c>
+      <c r="E1029" t="n">
+        <v>310.9</v>
+      </c>
+      <c r="F1029" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="G1029" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="n">
+        <v>70</v>
+      </c>
+      <c r="B1030" t="inlineStr">
+        <is>
+          <t>M-11-HRL</t>
+        </is>
+      </c>
+      <c r="C1030" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1030" t="n">
+        <v>409</v>
+      </c>
+      <c r="E1030" t="n">
+        <v>843</v>
+      </c>
+      <c r="F1030" t="n">
+        <v>434</v>
+      </c>
+      <c r="G1030" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="n">
+        <v>70</v>
+      </c>
+      <c r="B1031" t="inlineStr">
+        <is>
+          <t>M-22-HRL</t>
+        </is>
+      </c>
+      <c r="C1031" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1031" t="n">
+        <v>524</v>
+      </c>
+      <c r="E1031" t="n">
+        <v>339.1</v>
+      </c>
+      <c r="F1031" t="n">
+        <v>184.9</v>
+      </c>
+      <c r="G1031" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="n">
+        <v>70</v>
+      </c>
+      <c r="B1032" t="inlineStr">
+        <is>
+          <t>M-13-HRL</t>
+        </is>
+      </c>
+      <c r="C1032" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1032" t="n">
+        <v>562</v>
+      </c>
+      <c r="E1032" t="n">
+        <v>786</v>
+      </c>
+      <c r="F1032" t="n">
+        <v>224</v>
+      </c>
+      <c r="G1032" t="b">
         <v>1</v>
       </c>
     </row>
@@ -30387,7 +34829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -30529,18 +34971,90 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>63</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Vintage transfer C=0.500. Clean12 LOOCV=0.769. Extreme=0.875</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>8.6</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>66</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.788</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>IBS ratio=0.421. Best AUC at 240mo. Post-2000 bias=-32mo</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>8.7</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>69</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.788</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Compressed 2f C=0.769. Flags and papatzacos do not beat original 5f.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>8.8</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>70</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.788</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>P10-P90 coverage=8%. Outside: M-67-HRL, M-82-HRL, M-58-HRL, M-56-HRL, M-41-HRL, M-11-HRL</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>56</v>
-      </c>
-      <c r="C8" t="n">
+      <c r="B12" t="n">
+        <v>70</v>
+      </c>
+      <c r="C12" t="n">
         <v>0.788</v>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>5f Cox C=0.788</t>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>5f Cox C=0.788, vintage-transfer=0.500, coverage=8%</t>
         </is>
       </c>
     </row>
